--- a/models/9434_DCF_Model_20260906.xlsx
+++ b/models/9434_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C760B8A-424D-42F2-B169-504CFC588B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A0B320-6283-4D33-A92B-8A0FFC4019A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="360">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>DCF - Exit Multiple</t>
+  </si>
+  <si>
+    <t>コアDCF 1株値（フロア規則: 負または不成立なら 0）</t>
   </si>
   <si>
     <t>金融事業価値 [1株・別途加算]</t>
@@ -754,7 +757,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 11:16, template rev ab88046</t>
+    <t>Generated by pipeline on 2026-09-07 12:13, template rev 42941f3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -967,7 +970,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 11:16:18</t>
+    <t>2026-09-07 12:13:12</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1036,7 +1039,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>ab88046</t>
+    <t>42941f3</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1385,7 +1388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1444,6 +1447,7 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1766,7 +1770,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="B1:E32"/>
+  <dimension ref="B1:E33"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1775,19 +1779,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
     </row>
     <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -1831,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>(IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))+C18</f>
+        <f>C18+C19</f>
         <v>240</v>
       </c>
     </row>
@@ -1897,62 +1901,65 @@
         <v>-0.25167224080267553</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="44">
+        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))</f>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="45">
         <f>'Equity Method Value'!C17</f>
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="11">
-        <f>'Comps Analysis'!C27</f>
-        <v>182</v>
-      </c>
-      <c r="D19" s="7">
-        <f>IF(ISNUMBER(C18),(C18-C9)/C9,"N/A")</f>
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+    </row>
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="11">
+        <f>'Comps Analysis'!C28</f>
+        <v>179</v>
+      </c>
+      <c r="D21" s="7">
+        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
         <v>-0.93311036789297663</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-    </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="6" t="str">
+    </row>
+    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="6" t="str">
         <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
         <v>179 - 268</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+    <row r="25" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
@@ -1964,18 +1971,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B29" s="8" t="s">
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    </row>
+    <row r="30" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B30" s="8" t="s">
         <v>29</v>
       </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
@@ -1985,6 +1991,11 @@
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2013,25 +2024,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5">
         <v>6241290</v>
@@ -2042,7 +2053,7 @@
     </row>
     <row r="7" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5">
         <v>2889116</v>
@@ -2053,7 +2064,7 @@
     </row>
     <row r="8" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5">
         <f>C6-C7</f>
@@ -2066,7 +2077,7 @@
     </row>
     <row r="9" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7">
         <f>C8/C6</f>
@@ -2079,7 +2090,7 @@
     </row>
     <row r="10" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5">
         <v>1858709</v>
@@ -2090,7 +2101,7 @@
     </row>
     <row r="11" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="5">
         <v>947351</v>
@@ -2101,7 +2112,7 @@
     </row>
     <row r="12" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5">
         <v>526133</v>
@@ -2112,7 +2123,7 @@
     </row>
     <row r="13" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7">
         <f>C11/C6</f>
@@ -2125,7 +2136,7 @@
     </row>
     <row r="14" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="7">
         <f>C12/C6</f>
@@ -2138,10 +2149,10 @@
     </row>
     <row r="15" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="7">
         <f>(D6-C6)/C6</f>
@@ -2150,10 +2161,10 @@
     </row>
     <row r="16" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
         <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
       </c>
       <c r="D16" s="7">
         <f>(D11-C11)/C11</f>
@@ -2162,12 +2173,12 @@
     </row>
     <row r="18" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="5">
         <v>1367871</v>
@@ -2178,34 +2189,34 @@
     </row>
     <row r="20" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" s="5">
         <v>1435525</v>
@@ -2216,19 +2227,19 @@
     </row>
     <row r="27" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
     </row>
     <row r="28" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2252,12 +2263,12 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2267,7 +2278,7 @@
     </row>
     <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="7">
         <v>0.11307</v>
@@ -2275,7 +2286,7 @@
     </row>
     <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="7">
         <v>0.25</v>
@@ -2283,7 +2294,7 @@
     </row>
     <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="7">
         <v>2.9700000000000001E-2</v>
@@ -2291,7 +2302,7 @@
     </row>
     <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="12">
         <v>0.48699999999999999</v>
@@ -2299,7 +2310,7 @@
     </row>
     <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" s="7">
         <v>6.5000000000000002E-2</v>
@@ -2307,7 +2318,7 @@
     </row>
     <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="7">
         <v>0.01</v>
@@ -2315,7 +2326,7 @@
     </row>
     <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7">
         <v>0.01</v>
@@ -2323,7 +2334,7 @@
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="13">
         <v>0.58579999999999999</v>
@@ -2331,7 +2342,7 @@
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="7">
         <v>0.01</v>
@@ -2339,7 +2350,7 @@
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="14">
         <v>8.1</v>
@@ -2347,7 +2358,7 @@
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="15">
         <v>47833719783</v>
@@ -2355,7 +2366,7 @@
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="5">
         <v>6702096</v>
@@ -2363,7 +2374,7 @@
     </row>
     <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="5">
         <v>6659368</v>
@@ -2371,7 +2382,7 @@
     </row>
     <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" s="7">
         <v>0.11307</v>
@@ -2379,7 +2390,7 @@
     </row>
     <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -2387,7 +2398,7 @@
     </row>
     <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" s="5">
         <v>7038680</v>
@@ -2395,7 +2406,7 @@
     </row>
     <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -2405,7 +2416,7 @@
     </row>
     <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="16">
         <f>C7+C8*C9+C10</f>
@@ -2414,7 +2425,7 @@
     </row>
     <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="16">
         <f>1/(1+C12)</f>
@@ -2423,7 +2434,7 @@
     </row>
     <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="16">
         <f>C12/(1+C12)</f>
@@ -2432,7 +2443,7 @@
     </row>
     <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="16">
         <f>C23*C24+C11*C25</f>
@@ -2441,10 +2452,10 @@
     </row>
     <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D27" s="6">
         <f>MATCH(C27,B69:B73,0)</f>
@@ -2453,7 +2464,7 @@
     </row>
     <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2463,24 +2474,24 @@
     </row>
     <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="18">
         <f>CHOOSE($D$27,C69,C70,C71,C72,C73)</f>
@@ -2505,7 +2516,7 @@
     </row>
     <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" s="18">
         <f>CHOOSE($D$27,C76,C77,C78,C79,C80)</f>
@@ -2530,7 +2541,7 @@
     </row>
     <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32" s="18">
         <f>CHOOSE($D$27,C83,C84,C85,C86,C87)</f>
@@ -2555,7 +2566,7 @@
     </row>
     <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="5">
         <f>C17*(1+C30)</f>
@@ -2580,7 +2591,7 @@
     </row>
     <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="5">
         <f>C33*C31</f>
@@ -2605,7 +2616,7 @@
     </row>
     <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" s="19">
         <f>C33-C34</f>
@@ -2630,7 +2641,7 @@
     </row>
     <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="7">
         <f>C35/C33</f>
@@ -2655,7 +2666,7 @@
     </row>
     <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="5">
         <f>C33*C32</f>
@@ -2680,7 +2691,7 @@
     </row>
     <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" s="7">
         <f>(C35-C37)/C33</f>
@@ -2705,7 +2716,7 @@
     </row>
     <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="19">
         <f>C35-C37</f>
@@ -2730,7 +2741,7 @@
     </row>
     <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="5">
         <f>MAX(0,C39*C6)</f>
@@ -2755,7 +2766,7 @@
     </row>
     <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="19">
         <f>C39-C40</f>
@@ -2780,7 +2791,7 @@
     </row>
     <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="5">
         <f>C33*C18</f>
@@ -2805,7 +2816,7 @@
     </row>
     <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="5">
         <f>C33*C5</f>
@@ -2830,7 +2841,7 @@
     </row>
     <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="5">
         <f>'NWC Schedule'!D19</f>
@@ -2855,7 +2866,7 @@
     </row>
     <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="20">
         <f>C41+C42-C43-C44</f>
@@ -2880,7 +2891,7 @@
     </row>
     <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" s="21">
         <f>1/(1+C26)^(C19+0)</f>
@@ -2905,7 +2916,7 @@
     </row>
     <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="19">
         <f>C45*C46</f>
@@ -2930,7 +2941,7 @@
     </row>
     <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -2940,7 +2951,7 @@
     </row>
     <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="5">
         <f>SUM(C47:G47)</f>
@@ -2949,7 +2960,7 @@
     </row>
     <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" s="5">
         <f>G45*(1+C13)/(C26-C13)</f>
@@ -2958,7 +2969,7 @@
     </row>
     <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" s="5">
         <f>C51*G46</f>
@@ -2967,7 +2978,7 @@
     </row>
     <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C53" s="5">
         <f>C50+C52</f>
@@ -2976,7 +2987,7 @@
     </row>
     <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" s="5">
         <f>C53-C16</f>
@@ -2985,7 +2996,7 @@
     </row>
     <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C55" s="24">
         <f>ROUND(C54*1000000/C15,0)</f>
@@ -2994,7 +3005,7 @@
     </row>
     <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -3004,7 +3015,7 @@
     </row>
     <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="5">
         <f>C50</f>
@@ -3013,7 +3024,7 @@
     </row>
     <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C59" s="5">
         <f>G39+G42</f>
@@ -3022,7 +3033,7 @@
     </row>
     <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
@@ -3031,7 +3042,7 @@
     </row>
     <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
@@ -3040,7 +3051,7 @@
     </row>
     <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
@@ -3049,7 +3060,7 @@
     </row>
     <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
@@ -3058,7 +3069,7 @@
     </row>
     <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
@@ -3067,7 +3078,7 @@
     </row>
     <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
@@ -3077,29 +3088,29 @@
     </row>
     <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C69" s="26">
         <v>2.5000000000000001E-2</v>
@@ -3119,7 +3130,7 @@
     </row>
     <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" s="26">
         <v>0.04</v>
@@ -3139,7 +3150,7 @@
     </row>
     <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C71" s="26">
         <v>2.5000000000000001E-2</v>
@@ -3159,7 +3170,7 @@
     </row>
     <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C72" s="26">
         <v>0.01</v>
@@ -3179,7 +3190,7 @@
     </row>
     <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C73" s="26">
         <v>-0.01</v>
@@ -3199,12 +3210,12 @@
     </row>
     <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="26">
         <v>0.51919999999999999</v>
@@ -3224,7 +3235,7 @@
     </row>
     <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C77" s="26">
         <v>0.51919999999999999</v>
@@ -3244,7 +3255,7 @@
     </row>
     <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C78" s="26">
         <v>0.51919999999999999</v>
@@ -3264,7 +3275,7 @@
     </row>
     <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C79" s="26">
         <v>0.51919999999999999</v>
@@ -3284,7 +3295,7 @@
     </row>
     <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C80" s="26">
         <v>0.51919999999999999</v>
@@ -3304,12 +3315,12 @@
     </row>
     <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C83" s="26">
         <v>0.3372</v>
@@ -3329,7 +3340,7 @@
     </row>
     <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C84" s="26">
         <v>0.3286</v>
@@ -3349,7 +3360,7 @@
     </row>
     <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C85" s="26">
         <v>0.3372</v>
@@ -3369,7 +3380,7 @@
     </row>
     <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C86" s="26">
         <v>0.3473</v>
@@ -3389,7 +3400,7 @@
     </row>
     <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C87" s="26">
         <v>0.35730000000000001</v>
@@ -3433,17 +3444,17 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -3455,7 +3466,7 @@
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="15">
         <f>'Executive Summary'!C9</f>
@@ -3464,7 +3475,7 @@
     </row>
     <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="15">
         <f>'DCF Model'!C15</f>
@@ -3473,7 +3484,7 @@
     </row>
     <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="5">
         <f>C6*C7/1000000</f>
@@ -3482,7 +3493,7 @@
     </row>
     <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5">
         <f>'DCF Model'!C16</f>
@@ -3491,7 +3502,7 @@
     </row>
     <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="5">
         <f>C8+C9</f>
@@ -3500,7 +3511,7 @@
     </row>
     <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="16">
         <f>'DCF Model'!C26</f>
@@ -3509,7 +3520,7 @@
     </row>
     <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="16">
         <f>'DCF Model'!C13</f>
@@ -3518,7 +3529,7 @@
     </row>
     <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="16">
         <f>'DCF Model'!C6</f>
@@ -3527,7 +3538,7 @@
     </row>
     <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="27">
         <v>956286</v>
@@ -3535,7 +3546,7 @@
     </row>
     <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="27">
         <v>956286</v>
@@ -3543,7 +3554,7 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="5">
         <f>'DCF Model'!G33</f>
@@ -3552,7 +3563,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="5">
         <f>'DCF Model'!C53</f>
@@ -3561,7 +3572,7 @@
     </row>
     <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="26">
         <v>0.14360011340415491</v>
@@ -3569,7 +3580,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="5">
         <f>C10-C17</f>
@@ -3578,7 +3589,7 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="15">
         <f>IFERROR(ROUND(C19*1000000/C7,0),"N/A")</f>
@@ -3587,7 +3598,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -3599,12 +3610,12 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C24" s="5">
         <f>C10*(C11-C12)</f>
@@ -3613,7 +3624,7 @@
     </row>
     <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C25" s="5">
         <f>IFERROR(C24/(1-C13),"N/A")</f>
@@ -3622,7 +3633,7 @@
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="14">
         <f>IFERROR(C25/C15,"N/A")</f>
@@ -3631,7 +3642,7 @@
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C27" s="14">
         <f>IFERROR(C25/C14,"N/A")</f>
@@ -3640,7 +3651,7 @@
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" s="7">
         <f>IFERROR(C25/C16,"N/A")</f>
@@ -3649,7 +3660,7 @@
     </row>
     <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C29" s="5">
         <f>IFERROR(C25/C18,"N/A")</f>
@@ -3658,7 +3669,7 @@
     </row>
     <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -3670,20 +3681,20 @@
     </row>
     <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D36" s="29">
         <f>'DCF Model'!C26-0.02</f>
@@ -3708,12 +3719,12 @@
     </row>
     <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" s="30">
         <v>3</v>
@@ -3741,7 +3752,7 @@
     </row>
     <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C39" s="30">
         <v>5</v>
@@ -3769,7 +3780,7 @@
     </row>
     <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" s="30">
         <v>7</v>
@@ -3797,7 +3808,7 @@
     </row>
     <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C41" s="30">
         <v>10</v>
@@ -3825,12 +3836,12 @@
     </row>
     <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" s="30">
         <v>3</v>
@@ -3858,7 +3869,7 @@
     </row>
     <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C44" s="30">
         <v>5</v>
@@ -3886,7 +3897,7 @@
     </row>
     <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C45" s="30">
         <v>7</v>
@@ -3914,7 +3925,7 @@
     </row>
     <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C46" s="30">
         <v>10</v>
@@ -3942,7 +3953,7 @@
     </row>
     <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23"/>
@@ -3954,7 +3965,7 @@
     </row>
     <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C48" s="30">
         <v>3</v>
@@ -3982,7 +3993,7 @@
     </row>
     <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C49" s="30">
         <v>5</v>
@@ -4010,7 +4021,7 @@
     </row>
     <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C50" s="30">
         <v>7</v>
@@ -4038,7 +4049,7 @@
     </row>
     <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C51" s="30">
         <v>10</v>
@@ -4066,7 +4077,7 @@
     </row>
     <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="23"/>
@@ -4078,7 +4089,7 @@
     </row>
     <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C53" s="30">
         <v>3</v>
@@ -4106,7 +4117,7 @@
     </row>
     <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C54" s="30">
         <v>5</v>
@@ -4134,7 +4145,7 @@
     </row>
     <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C55" s="30">
         <v>7</v>
@@ -4162,7 +4173,7 @@
     </row>
     <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C56" s="30">
         <v>10</v>
@@ -4190,7 +4201,7 @@
     </row>
     <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -4202,12 +4213,12 @@
     </row>
     <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C60" s="5">
         <f>F49</f>
@@ -4216,13 +4227,13 @@
     </row>
     <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
@@ -4253,7 +4264,7 @@
     </row>
     <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C65" s="5">
         <f>IFERROR($C$60/$C$18,"N/A")</f>
@@ -4292,7 +4303,7 @@
     </row>
     <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -4304,7 +4315,7 @@
     </row>
     <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C70" s="14">
         <f>IFERROR(C10/'Comps Analysis'!G5,"N/A")</f>
@@ -4313,7 +4324,7 @@
     </row>
     <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" s="14">
         <f>IFERROR(C10/'Comps Analysis'!F5,"N/A")</f>
@@ -4322,7 +4333,7 @@
     </row>
     <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" s="14">
         <f>IFERROR(C10/(C25+'DCF Model'!G42),"N/A")</f>
@@ -4331,7 +4342,7 @@
     </row>
     <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" s="14">
         <f>IFERROR(C10/(C60+'DCF Model'!G42),"N/A")</f>
@@ -4340,7 +4351,7 @@
     </row>
     <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C74" s="14">
         <f>IFERROR('Comps Analysis'!D16,"N/A")</f>
@@ -4349,12 +4360,12 @@
     </row>
     <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C77" s="23"/>
       <c r="D77" s="23"/>
@@ -4397,35 +4408,35 @@
   <sheetData>
     <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" s="34">
         <f>C18/C9</f>
@@ -4454,53 +4465,53 @@
     </row>
     <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -4511,7 +4522,7 @@
     </row>
     <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="36">
         <v>6659368</v>
@@ -4539,30 +4550,30 @@
     </row>
     <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -4573,122 +4584,122 @@
     </row>
     <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -4699,7 +4710,7 @@
     </row>
     <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="20">
         <v>-27189</v>
@@ -4727,10 +4738,10 @@
     </row>
     <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="24">
         <f>D18-C18</f>
@@ -4755,7 +4766,7 @@
     </row>
     <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -4766,29 +4777,29 @@
     </row>
     <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="26">
         <v>0</v>
@@ -4808,7 +4819,7 @@
     </row>
     <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" s="26">
         <v>0</v>
@@ -4828,7 +4839,7 @@
     </row>
     <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="26">
         <v>0</v>
@@ -4848,7 +4859,7 @@
     </row>
     <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D28" s="26">
         <v>0</v>
@@ -4868,7 +4879,7 @@
     </row>
     <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" s="26">
         <v>0</v>
@@ -4909,12 +4920,12 @@
   <sheetData>
     <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
@@ -4925,54 +4936,54 @@
         <v>5</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="38">
         <f>'Executive Summary'!C9*C23/1000000</f>
@@ -5024,10 +5035,10 @@
     </row>
     <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6" s="38">
         <v>13985423</v>
@@ -5077,10 +5088,10 @@
     </row>
     <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7" s="38">
         <v>11017665</v>
@@ -5130,10 +5141,10 @@
     </row>
     <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D8" s="38">
         <v>382283</v>
@@ -5183,12 +5194,12 @@
     </row>
     <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D15" s="39">
         <f t="shared" ref="D15:I15" si="0">PERCENTILE(J6:J8,0.25)</f>
@@ -5217,7 +5228,7 @@
     </row>
     <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D16" s="39">
         <f t="shared" ref="D16:I16" si="1">MEDIAN(J6:J8)</f>
@@ -5246,7 +5257,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D17" s="39">
         <f t="shared" ref="D17:I17" si="2">PERCENTILE(J6:J8,0.75)</f>
@@ -5275,7 +5286,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -5287,12 +5298,12 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C21" s="5">
         <v>1709261</v>
@@ -5300,7 +5311,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="5">
         <v>550759</v>
@@ -5308,7 +5319,7 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="15">
         <v>47833719783</v>
@@ -5316,7 +5327,7 @@
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="5">
         <v>6702096</v>
@@ -5324,12 +5335,12 @@
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C27" s="24">
         <f>ROUND((C21*D16-C24)*1000000/C23,0)</f>
@@ -5338,7 +5349,7 @@
     </row>
     <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" s="24">
         <f>ROUND(C22*F16*1000000/C23,0)</f>
@@ -5366,26 +5377,26 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C3" s="16">
         <f>'DCF Model'!C26</f>
         <v>4.8690250977424653E-2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F3" s="16">
         <f>'DCF Model'!C13</f>
         <v>0.01</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I3" s="14">
         <f>'DCF Model'!C14</f>
@@ -5394,12 +5405,12 @@
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C6" s="42">
         <f>$F$3-0.0075</f>
@@ -5670,12 +5681,12 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C17" s="43">
         <f>$I$3-3</f>
@@ -5945,16 +5956,16 @@
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
+      <c r="B26" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5983,165 +5994,165 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" t="s">
         <v>239</v>
       </c>
-      <c r="E5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" t="s">
-        <v>238</v>
-      </c>
       <c r="G5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -6149,324 +6160,324 @@
     </row>
     <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C36" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C38" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C44" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C45" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C52" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C53" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C54" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C55" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C57" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C61" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6474,10 +6485,10 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C66" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -6501,125 +6512,125 @@
   <sheetData>
     <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="45" t="s">
-        <v>342</v>
+      <c r="B3" s="46" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>344</v>
-      </c>
-      <c r="E6" s="46" t="s">
+      <c r="D6" s="47" t="s">
         <v>345</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="E6" s="47" t="s">
         <v>346</v>
       </c>
+      <c r="F6" s="47" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="7" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="47" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="D7" s="48">
+      <c r="C7" s="48" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" s="49">
         <v>1796086</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="50">
         <v>0.40799999999999997</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="51">
         <f>D7*E7</f>
         <v>732803.08799999999</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="51" t="s">
-        <v>349</v>
-      </c>
-      <c r="F8" s="52">
+      <c r="B8" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="F8" s="53">
         <f>SUM(F7:F7)</f>
         <v>732803.08799999999</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="47" t="s">
-        <v>351</v>
-      </c>
-      <c r="C11" s="53">
+      <c r="B11" s="48" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="54">
         <f>F8</f>
         <v>732803.08799999999</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="47" t="s">
-        <v>352</v>
-      </c>
-      <c r="C12" s="48">
+      <c r="B12" s="48" t="s">
+        <v>353</v>
+      </c>
+      <c r="C12" s="49">
         <v>44705</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="14" x14ac:dyDescent="0.3">
-      <c r="B13" s="51" t="s">
-        <v>353</v>
-      </c>
-      <c r="C13" s="52">
+      <c r="B13" s="52" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="53">
         <f>C11+C12</f>
         <v>777508.08799999999</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="54" t="s">
-        <v>354</v>
+      <c r="B14" s="55" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="C16" s="55">
+      <c r="B16" s="48" t="s">
+        <v>356</v>
+      </c>
+      <c r="C16" s="56">
         <f>'DCF Model'!C15</f>
         <v>47833719783</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B17" s="51" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="52">
+      <c r="B17" s="52" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" s="53">
         <f>ROUND(C13/C16*1000000,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="45" t="s">
-        <v>357</v>
+      <c r="B19" s="46" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B20" s="45" t="s">
-        <v>358</v>
+      <c r="B20" s="46" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/models/9434_DCF_Model_20260906.xlsx
+++ b/models/9434_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A0B320-6283-4D33-A92B-8A0FFC4019A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A88D7CC-C289-41CB-B446-8B2251FA2B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="360">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Current Price</t>
   </si>
   <si>
-    <t>Target Price (コアDCF + 金融事業価値)</t>
+    <t>Target Price (コアDCF[フロア適用] + 金融事業価値)</t>
   </si>
   <si>
     <t>Recommendation</t>
@@ -87,22 +87,19 @@
     <t>DCF - Exit Multiple</t>
   </si>
   <si>
-    <t>コアDCF 1株値（フロア規則: 負または不成立なら 0）</t>
+    <t>Comps - EV/EBITDA Median [参考・Target不算入]</t>
+  </si>
+  <si>
+    <t>Comps - PER Median [参考・Target不算入]</t>
+  </si>
+  <si>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【型F: 持分法主導】コア営業利益 = 売上総利益 − 販売費及び一般管理費 で定義し、持分法投資損益・受取配当金・金融損益・投資損益をコアから除外している。除外した持分法投資の価値は上の別途加算行で加算する（二重計上なし）。持分法投資価値の算定方式は 'market_stakes'、詳細は Equity Method Value シート。Comps は EV 倍率が持分法混在で歪むため PER/PBR を参照とする。</t>
+  </si>
+  <si>
+    <t>DCF Valuation Range (PGM - Exit)</t>
   </si>
   <si>
     <t>金融事業価値 [1株・別途加算]</t>
-  </si>
-  <si>
-    <t>Comps - EV/EBITDA Median [参考・Target不算入]</t>
-  </si>
-  <si>
-    <t>Comps - PER Median [参考・Target不算入]</t>
-  </si>
-  <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【型F: 持分法主導】コア営業利益 = 売上総利益 − 販売費及び一般管理費 で定義し、持分法投資損益・受取配当金・金融損益・投資損益をコアから除外している。除外した持分法投資の価値は上の別途加算行で加算する（二重計上なし）。持分法投資価値の算定方式は 'market_stakes'、詳細は Equity Method Value シート。Comps は EV 倍率が持分法混在で歪むため PER/PBR を参照とする。</t>
-  </si>
-  <si>
-    <t>DCF Valuation Range (PGM - Exit)</t>
   </si>
   <si>
     <t>Key Investment Thesis</t>
@@ -757,7 +754,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 12:13, template rev 42941f3</t>
+    <t>Generated by pipeline on 2026-09-07 13:02, template rev b0a6ac9</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -970,7 +967,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 12:13:12</t>
+    <t>2026-09-07 13:02:26</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1039,7 +1036,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>42941f3</t>
+    <t>b0a6ac9</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1055,6 +1052,9 @@
   </si>
   <si>
     <t>equity_method_multiple</t>
+  </si>
+  <si>
+    <t>equity_method_fair_value_based</t>
   </si>
   <si>
     <t>equity_method_basis</t>
@@ -1388,7 +1388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1447,7 +1447,6 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1770,7 +1769,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="B1:E33"/>
+  <dimension ref="B1:E31"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1779,19 +1778,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -1835,7 +1834,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>C18+C19</f>
+        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22</f>
         <v>240</v>
       </c>
     </row>
@@ -1901,101 +1900,100 @@
         <v>-0.25167224080267553</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="44">
-        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))</f>
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="11">
+        <f>'Comps Analysis'!C27</f>
+        <v>182</v>
+      </c>
+      <c r="D18" s="7">
+        <f>IF(ISNUMBER(C18),(C18-C9)/C9,"N/A")</f>
+        <v>-0.23913043478260865</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="11">
+        <f>'Comps Analysis'!C28</f>
+        <v>179</v>
+      </c>
+      <c r="D19" s="7">
+        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
+        <v>-0.25167224080267553</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+    </row>
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
+        <v>179 - 268</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="44">
         <f>'Equity Method Value'!C17</f>
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-    </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="11">
-        <f>'Comps Analysis'!C28</f>
-        <v>179</v>
-      </c>
-      <c r="D21" s="7">
-        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
-        <v>-0.93311036789297663</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="6" t="str">
-        <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
-        <v>179 - 268</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B30" s="8" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2024,25 +2022,25 @@
   <sheetData>
     <row r="2" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="5">
         <v>6241290</v>
@@ -2053,7 +2051,7 @@
     </row>
     <row r="7" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="5">
         <v>2889116</v>
@@ -2064,7 +2062,7 @@
     </row>
     <row r="8" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="5">
         <f>C6-C7</f>
@@ -2077,7 +2075,7 @@
     </row>
     <row r="9" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="7">
         <f>C8/C6</f>
@@ -2090,7 +2088,7 @@
     </row>
     <row r="10" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5">
         <v>1858709</v>
@@ -2101,7 +2099,7 @@
     </row>
     <row r="11" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5">
         <v>947351</v>
@@ -2112,7 +2110,7 @@
     </row>
     <row r="12" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5">
         <v>526133</v>
@@ -2123,7 +2121,7 @@
     </row>
     <row r="13" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="7">
         <f>C11/C6</f>
@@ -2136,7 +2134,7 @@
     </row>
     <row r="14" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="7">
         <f>C12/C6</f>
@@ -2149,10 +2147,10 @@
     </row>
     <row r="15" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
         <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
       </c>
       <c r="D15" s="7">
         <f>(D6-C6)/C6</f>
@@ -2161,10 +2159,10 @@
     </row>
     <row r="16" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="7">
         <f>(D11-C11)/C11</f>
@@ -2173,12 +2171,12 @@
     </row>
     <row r="18" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="5">
         <v>1367871</v>
@@ -2189,34 +2187,34 @@
     </row>
     <row r="20" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="5">
         <v>1435525</v>
@@ -2227,19 +2225,19 @@
     </row>
     <row r="27" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
     </row>
     <row r="28" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2263,12 +2261,12 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2278,7 +2276,7 @@
     </row>
     <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="7">
         <v>0.11307</v>
@@ -2286,7 +2284,7 @@
     </row>
     <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" s="7">
         <v>0.25</v>
@@ -2294,7 +2292,7 @@
     </row>
     <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="7">
         <v>2.9700000000000001E-2</v>
@@ -2302,7 +2300,7 @@
     </row>
     <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="12">
         <v>0.48699999999999999</v>
@@ -2310,7 +2308,7 @@
     </row>
     <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7">
         <v>6.5000000000000002E-2</v>
@@ -2318,7 +2316,7 @@
     </row>
     <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="7">
         <v>0.01</v>
@@ -2326,7 +2324,7 @@
     </row>
     <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7">
         <v>0.01</v>
@@ -2334,7 +2332,7 @@
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="13">
         <v>0.58579999999999999</v>
@@ -2342,7 +2340,7 @@
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" s="7">
         <v>0.01</v>
@@ -2350,7 +2348,7 @@
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="14">
         <v>8.1</v>
@@ -2358,7 +2356,7 @@
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="15">
         <v>47833719783</v>
@@ -2366,7 +2364,7 @@
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C16" s="5">
         <v>6702096</v>
@@ -2374,7 +2372,7 @@
     </row>
     <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="5">
         <v>6659368</v>
@@ -2382,7 +2380,7 @@
     </row>
     <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="7">
         <v>0.11307</v>
@@ -2390,7 +2388,7 @@
     </row>
     <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -2398,7 +2396,7 @@
     </row>
     <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="5">
         <v>7038680</v>
@@ -2406,7 +2404,7 @@
     </row>
     <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -2416,7 +2414,7 @@
     </row>
     <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" s="16">
         <f>C7+C8*C9+C10</f>
@@ -2425,7 +2423,7 @@
     </row>
     <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="16">
         <f>1/(1+C12)</f>
@@ -2434,7 +2432,7 @@
     </row>
     <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="16">
         <f>C12/(1+C12)</f>
@@ -2443,7 +2441,7 @@
     </row>
     <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="16">
         <f>C23*C24+C11*C25</f>
@@ -2452,10 +2450,10 @@
     </row>
     <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>82</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>83</v>
       </c>
       <c r="D27" s="6">
         <f>MATCH(C27,B69:B73,0)</f>
@@ -2464,7 +2462,7 @@
     </row>
     <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2474,24 +2472,24 @@
     </row>
     <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="E29" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" s="18">
         <f>CHOOSE($D$27,C69,C70,C71,C72,C73)</f>
@@ -2516,7 +2514,7 @@
     </row>
     <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="18">
         <f>CHOOSE($D$27,C76,C77,C78,C79,C80)</f>
@@ -2541,7 +2539,7 @@
     </row>
     <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C32" s="18">
         <f>CHOOSE($D$27,C83,C84,C85,C86,C87)</f>
@@ -2566,7 +2564,7 @@
     </row>
     <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="5">
         <f>C17*(1+C30)</f>
@@ -2591,7 +2589,7 @@
     </row>
     <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="5">
         <f>C33*C31</f>
@@ -2616,7 +2614,7 @@
     </row>
     <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="19">
         <f>C33-C34</f>
@@ -2641,7 +2639,7 @@
     </row>
     <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="7">
         <f>C35/C33</f>
@@ -2666,7 +2664,7 @@
     </row>
     <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" s="5">
         <f>C33*C32</f>
@@ -2691,7 +2689,7 @@
     </row>
     <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C38" s="7">
         <f>(C35-C37)/C33</f>
@@ -2716,7 +2714,7 @@
     </row>
     <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C39" s="19">
         <f>C35-C37</f>
@@ -2741,7 +2739,7 @@
     </row>
     <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C40" s="5">
         <f>MAX(0,C39*C6)</f>
@@ -2766,7 +2764,7 @@
     </row>
     <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C41" s="19">
         <f>C39-C40</f>
@@ -2791,7 +2789,7 @@
     </row>
     <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C42" s="5">
         <f>C33*C18</f>
@@ -2816,7 +2814,7 @@
     </row>
     <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C43" s="5">
         <f>C33*C5</f>
@@ -2841,7 +2839,7 @@
     </row>
     <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" s="5">
         <f>'NWC Schedule'!D19</f>
@@ -2866,7 +2864,7 @@
     </row>
     <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C45" s="20">
         <f>C41+C42-C43-C44</f>
@@ -2891,7 +2889,7 @@
     </row>
     <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C46" s="21">
         <f>1/(1+C26)^(C19+0)</f>
@@ -2916,7 +2914,7 @@
     </row>
     <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C47" s="19">
         <f>C45*C46</f>
@@ -2941,7 +2939,7 @@
     </row>
     <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -2951,7 +2949,7 @@
     </row>
     <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C50" s="5">
         <f>SUM(C47:G47)</f>
@@ -2960,7 +2958,7 @@
     </row>
     <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C51" s="5">
         <f>G45*(1+C13)/(C26-C13)</f>
@@ -2969,7 +2967,7 @@
     </row>
     <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C52" s="5">
         <f>C51*G46</f>
@@ -2978,7 +2976,7 @@
     </row>
     <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" s="5">
         <f>C50+C52</f>
@@ -2987,7 +2985,7 @@
     </row>
     <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="5">
         <f>C53-C16</f>
@@ -2996,7 +2994,7 @@
     </row>
     <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C55" s="24">
         <f>ROUND(C54*1000000/C15,0)</f>
@@ -3005,7 +3003,7 @@
     </row>
     <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -3015,7 +3013,7 @@
     </row>
     <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C58" s="5">
         <f>C50</f>
@@ -3024,7 +3022,7 @@
     </row>
     <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C59" s="5">
         <f>G39+G42</f>
@@ -3033,7 +3031,7 @@
     </row>
     <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
@@ -3042,7 +3040,7 @@
     </row>
     <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
@@ -3051,7 +3049,7 @@
     </row>
     <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
@@ -3060,7 +3058,7 @@
     </row>
     <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
@@ -3069,7 +3067,7 @@
     </row>
     <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
@@ -3078,7 +3076,7 @@
     </row>
     <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
@@ -3088,29 +3086,29 @@
     </row>
     <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="D67" s="25" t="s">
+      <c r="E67" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="E67" s="25" t="s">
+      <c r="F67" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="F67" s="25" t="s">
+      <c r="G67" s="25" t="s">
         <v>118</v>
-      </c>
-      <c r="G67" s="25" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C69" s="26">
         <v>2.5000000000000001E-2</v>
@@ -3130,7 +3128,7 @@
     </row>
     <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C70" s="26">
         <v>0.04</v>
@@ -3150,7 +3148,7 @@
     </row>
     <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C71" s="26">
         <v>2.5000000000000001E-2</v>
@@ -3170,7 +3168,7 @@
     </row>
     <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C72" s="26">
         <v>0.01</v>
@@ -3190,7 +3188,7 @@
     </row>
     <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C73" s="26">
         <v>-0.01</v>
@@ -3210,12 +3208,12 @@
     </row>
     <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C76" s="26">
         <v>0.51919999999999999</v>
@@ -3235,7 +3233,7 @@
     </row>
     <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C77" s="26">
         <v>0.51919999999999999</v>
@@ -3255,7 +3253,7 @@
     </row>
     <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C78" s="26">
         <v>0.51919999999999999</v>
@@ -3275,7 +3273,7 @@
     </row>
     <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C79" s="26">
         <v>0.51919999999999999</v>
@@ -3295,7 +3293,7 @@
     </row>
     <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C80" s="26">
         <v>0.51919999999999999</v>
@@ -3315,12 +3313,12 @@
     </row>
     <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C83" s="26">
         <v>0.3372</v>
@@ -3340,7 +3338,7 @@
     </row>
     <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C84" s="26">
         <v>0.3286</v>
@@ -3360,7 +3358,7 @@
     </row>
     <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C85" s="26">
         <v>0.3372</v>
@@ -3380,7 +3378,7 @@
     </row>
     <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C86" s="26">
         <v>0.3473</v>
@@ -3400,7 +3398,7 @@
     </row>
     <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C87" s="26">
         <v>0.35730000000000001</v>
@@ -3444,17 +3442,17 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -3466,7 +3464,7 @@
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="15">
         <f>'Executive Summary'!C9</f>
@@ -3475,7 +3473,7 @@
     </row>
     <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="15">
         <f>'DCF Model'!C15</f>
@@ -3484,7 +3482,7 @@
     </row>
     <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="5">
         <f>C6*C7/1000000</f>
@@ -3493,7 +3491,7 @@
     </row>
     <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" s="5">
         <f>'DCF Model'!C16</f>
@@ -3502,7 +3500,7 @@
     </row>
     <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" s="5">
         <f>C8+C9</f>
@@ -3511,7 +3509,7 @@
     </row>
     <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C11" s="16">
         <f>'DCF Model'!C26</f>
@@ -3520,7 +3518,7 @@
     </row>
     <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="16">
         <f>'DCF Model'!C13</f>
@@ -3529,7 +3527,7 @@
     </row>
     <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="16">
         <f>'DCF Model'!C6</f>
@@ -3538,7 +3536,7 @@
     </row>
     <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="27">
         <v>956286</v>
@@ -3546,7 +3544,7 @@
     </row>
     <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="27">
         <v>956286</v>
@@ -3554,7 +3552,7 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="5">
         <f>'DCF Model'!G33</f>
@@ -3563,7 +3561,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="5">
         <f>'DCF Model'!C53</f>
@@ -3572,7 +3570,7 @@
     </row>
     <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="26">
         <v>0.14360011340415491</v>
@@ -3580,7 +3578,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C19" s="5">
         <f>C10-C17</f>
@@ -3589,7 +3587,7 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C20" s="15">
         <f>IFERROR(ROUND(C19*1000000/C7,0),"N/A")</f>
@@ -3598,7 +3596,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -3610,12 +3608,12 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C24" s="5">
         <f>C10*(C11-C12)</f>
@@ -3624,7 +3622,7 @@
     </row>
     <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25" s="5">
         <f>IFERROR(C24/(1-C13),"N/A")</f>
@@ -3633,7 +3631,7 @@
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="14">
         <f>IFERROR(C25/C15,"N/A")</f>
@@ -3642,7 +3640,7 @@
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C27" s="14">
         <f>IFERROR(C25/C14,"N/A")</f>
@@ -3651,7 +3649,7 @@
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C28" s="7">
         <f>IFERROR(C25/C16,"N/A")</f>
@@ -3660,7 +3658,7 @@
     </row>
     <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" s="5">
         <f>IFERROR(C25/C18,"N/A")</f>
@@ -3669,7 +3667,7 @@
     </row>
     <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -3681,20 +3679,20 @@
     </row>
     <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="28" t="s">
         <v>151</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>152</v>
       </c>
       <c r="D36" s="29">
         <f>'DCF Model'!C26-0.02</f>
@@ -3719,12 +3717,12 @@
     </row>
     <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C38" s="30">
         <v>3</v>
@@ -3752,7 +3750,7 @@
     </row>
     <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C39" s="30">
         <v>5</v>
@@ -3780,7 +3778,7 @@
     </row>
     <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" s="30">
         <v>7</v>
@@ -3808,7 +3806,7 @@
     </row>
     <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="30">
         <v>10</v>
@@ -3836,12 +3834,12 @@
     </row>
     <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="30">
         <v>3</v>
@@ -3869,7 +3867,7 @@
     </row>
     <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C44" s="30">
         <v>5</v>
@@ -3897,7 +3895,7 @@
     </row>
     <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C45" s="30">
         <v>7</v>
@@ -3925,7 +3923,7 @@
     </row>
     <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C46" s="30">
         <v>10</v>
@@ -3953,7 +3951,7 @@
     </row>
     <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23"/>
@@ -3965,7 +3963,7 @@
     </row>
     <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C48" s="30">
         <v>3</v>
@@ -3993,7 +3991,7 @@
     </row>
     <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C49" s="30">
         <v>5</v>
@@ -4021,7 +4019,7 @@
     </row>
     <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C50" s="30">
         <v>7</v>
@@ -4049,7 +4047,7 @@
     </row>
     <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" s="30">
         <v>10</v>
@@ -4077,7 +4075,7 @@
     </row>
     <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="23"/>
@@ -4089,7 +4087,7 @@
     </row>
     <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C53" s="30">
         <v>3</v>
@@ -4117,7 +4115,7 @@
     </row>
     <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C54" s="30">
         <v>5</v>
@@ -4145,7 +4143,7 @@
     </row>
     <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C55" s="30">
         <v>7</v>
@@ -4173,7 +4171,7 @@
     </row>
     <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" s="30">
         <v>10</v>
@@ -4201,7 +4199,7 @@
     </row>
     <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -4213,12 +4211,12 @@
     </row>
     <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C60" s="5">
         <f>F49</f>
@@ -4227,13 +4225,13 @@
     </row>
     <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="D62" s="28" t="s">
         <v>165</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
@@ -4264,7 +4262,7 @@
     </row>
     <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="5">
         <f>IFERROR($C$60/$C$18,"N/A")</f>
@@ -4303,7 +4301,7 @@
     </row>
     <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -4315,7 +4313,7 @@
     </row>
     <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C70" s="14">
         <f>IFERROR(C10/'Comps Analysis'!G5,"N/A")</f>
@@ -4324,7 +4322,7 @@
     </row>
     <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="14">
         <f>IFERROR(C10/'Comps Analysis'!F5,"N/A")</f>
@@ -4333,7 +4331,7 @@
     </row>
     <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C72" s="14">
         <f>IFERROR(C10/(C25+'DCF Model'!G42),"N/A")</f>
@@ -4342,7 +4340,7 @@
     </row>
     <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C73" s="14">
         <f>IFERROR(C10/(C60+'DCF Model'!G42),"N/A")</f>
@@ -4351,7 +4349,7 @@
     </row>
     <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C74" s="14">
         <f>IFERROR('Comps Analysis'!D16,"N/A")</f>
@@ -4360,12 +4358,12 @@
     </row>
     <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" s="23"/>
       <c r="D77" s="23"/>
@@ -4408,35 +4406,35 @@
   <sheetData>
     <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="32" t="s">
-        <v>178</v>
-      </c>
       <c r="D4" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="F4" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="G4" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="32" t="s">
         <v>88</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5" s="34">
         <f>C18/C9</f>
@@ -4465,53 +4463,53 @@
     </row>
     <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -4522,7 +4520,7 @@
     </row>
     <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="36">
         <v>6659368</v>
@@ -4550,30 +4548,30 @@
     </row>
     <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -4584,122 +4582,122 @@
     </row>
     <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -4710,7 +4708,7 @@
     </row>
     <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C18" s="20">
         <v>-27189</v>
@@ -4738,10 +4736,10 @@
     </row>
     <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="24">
         <f>D18-C18</f>
@@ -4766,7 +4764,7 @@
     </row>
     <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -4777,29 +4775,29 @@
     </row>
     <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="F23" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="G23" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="H23" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="26">
         <v>0</v>
@@ -4819,7 +4817,7 @@
     </row>
     <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" s="26">
         <v>0</v>
@@ -4839,7 +4837,7 @@
     </row>
     <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" s="26">
         <v>0</v>
@@ -4859,7 +4857,7 @@
     </row>
     <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="26">
         <v>0</v>
@@ -4879,7 +4877,7 @@
     </row>
     <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D29" s="26">
         <v>0</v>
@@ -4920,12 +4918,12 @@
   <sheetData>
     <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
@@ -4936,54 +4934,54 @@
         <v>5</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="L4" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="M4" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="N4" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="O4" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="P4" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="Q4" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" t="s">
         <v>202</v>
-      </c>
-      <c r="C5" t="s">
-        <v>203</v>
       </c>
       <c r="D5" s="38">
         <f>'Executive Summary'!C9*C23/1000000</f>
@@ -5035,10 +5033,10 @@
     </row>
     <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" t="s">
         <v>204</v>
-      </c>
-      <c r="C6" t="s">
-        <v>205</v>
       </c>
       <c r="D6" s="38">
         <v>13985423</v>
@@ -5088,10 +5086,10 @@
     </row>
     <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" t="s">
         <v>206</v>
-      </c>
-      <c r="C7" t="s">
-        <v>207</v>
       </c>
       <c r="D7" s="38">
         <v>11017665</v>
@@ -5141,10 +5139,10 @@
     </row>
     <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" t="s">
         <v>208</v>
-      </c>
-      <c r="C8" t="s">
-        <v>209</v>
       </c>
       <c r="D8" s="38">
         <v>382283</v>
@@ -5194,12 +5192,12 @@
     </row>
     <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D15" s="39">
         <f t="shared" ref="D15:I15" si="0">PERCENTILE(J6:J8,0.25)</f>
@@ -5228,7 +5226,7 @@
     </row>
     <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D16" s="39">
         <f t="shared" ref="D16:I16" si="1">MEDIAN(J6:J8)</f>
@@ -5257,7 +5255,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D17" s="39">
         <f t="shared" ref="D17:I17" si="2">PERCENTILE(J6:J8,0.75)</f>
@@ -5286,7 +5284,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -5298,12 +5296,12 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="5">
         <v>1709261</v>
@@ -5311,7 +5309,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="5">
         <v>550759</v>
@@ -5319,7 +5317,7 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C23" s="15">
         <v>47833719783</v>
@@ -5327,7 +5325,7 @@
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="5">
         <v>6702096</v>
@@ -5335,12 +5333,12 @@
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C27" s="24">
         <f>ROUND((C21*D16-C24)*1000000/C23,0)</f>
@@ -5349,7 +5347,7 @@
     </row>
     <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C28" s="24">
         <f>ROUND(C22*F16*1000000/C23,0)</f>
@@ -5377,26 +5375,26 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" s="16">
         <f>'DCF Model'!C26</f>
         <v>4.8690250977424653E-2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F3" s="16">
         <f>'DCF Model'!C13</f>
         <v>0.01</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I3" s="14">
         <f>'DCF Model'!C14</f>
@@ -5405,12 +5403,12 @@
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C6" s="42">
         <f>$F$3-0.0075</f>
@@ -5681,12 +5679,12 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C17" s="43">
         <f>$I$3-3</f>
@@ -5956,16 +5954,16 @@
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="59" t="s">
-        <v>230</v>
-      </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="B26" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5981,7 +5979,7 @@
   <sheetPr>
     <tabColor rgb="FF808080"/>
   </sheetPr>
-  <dimension ref="B2:G66"/>
+  <dimension ref="B2:G67"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -5994,165 +5992,165 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" t="s">
         <v>238</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>239</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>240</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G5" t="s">
         <v>241</v>
-      </c>
-      <c r="F5" t="s">
-        <v>239</v>
-      </c>
-      <c r="G5" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" t="s">
         <v>243</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>244</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>245</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>246</v>
-      </c>
-      <c r="G6" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" t="s">
         <v>251</v>
-      </c>
-      <c r="C14" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C15" t="s">
         <v>253</v>
-      </c>
-      <c r="C15" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" t="s">
         <v>255</v>
-      </c>
-      <c r="C16" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" t="s">
         <v>257</v>
-      </c>
-      <c r="C17" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" t="s">
         <v>260</v>
-      </c>
-      <c r="C19" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" t="s">
         <v>262</v>
-      </c>
-      <c r="C20" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" t="s">
         <v>264</v>
-      </c>
-      <c r="C21" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" t="s">
         <v>266</v>
-      </c>
-      <c r="C22" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -6160,324 +6158,324 @@
     </row>
     <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C26" t="s">
         <v>271</v>
-      </c>
-      <c r="C26" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" t="s">
         <v>275</v>
-      </c>
-      <c r="C29" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C30" t="s">
         <v>277</v>
-      </c>
-      <c r="C30" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C31" t="s">
         <v>279</v>
-      </c>
-      <c r="C31" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C34" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C35" t="s">
         <v>284</v>
-      </c>
-      <c r="C35" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C36" t="s">
         <v>286</v>
-      </c>
-      <c r="C36" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" t="s">
         <v>288</v>
-      </c>
-      <c r="C37" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C38" t="s">
         <v>290</v>
-      </c>
-      <c r="C38" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C39" t="s">
         <v>292</v>
-      </c>
-      <c r="C39" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C40" t="s">
         <v>294</v>
-      </c>
-      <c r="C40" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" t="s">
         <v>298</v>
-      </c>
-      <c r="C43" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C44" t="s">
         <v>300</v>
-      </c>
-      <c r="C44" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C45" t="s">
         <v>302</v>
-      </c>
-      <c r="C45" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C46" t="s">
         <v>304</v>
-      </c>
-      <c r="C46" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C47" t="s">
         <v>306</v>
-      </c>
-      <c r="C47" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C48" t="s">
         <v>308</v>
-      </c>
-      <c r="C48" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C49" t="s">
         <v>310</v>
-      </c>
-      <c r="C49" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" t="s">
         <v>312</v>
-      </c>
-      <c r="C50" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C51" t="s">
         <v>314</v>
-      </c>
-      <c r="C51" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C52" t="s">
         <v>316</v>
-      </c>
-      <c r="C52" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C53" t="s">
         <v>318</v>
-      </c>
-      <c r="C53" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C54" t="s">
         <v>320</v>
-      </c>
-      <c r="C54" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C55" t="s">
         <v>322</v>
-      </c>
-      <c r="C55" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C57" t="s">
         <v>325</v>
-      </c>
-      <c r="C57" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C58" t="s">
         <v>327</v>
-      </c>
-      <c r="C58" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C59" t="s">
         <v>329</v>
-      </c>
-      <c r="C59" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C60" t="s">
         <v>331</v>
-      </c>
-      <c r="C60" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" t="s">
         <v>333</v>
-      </c>
-      <c r="C61" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C62" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
+        <v>335</v>
+      </c>
+      <c r="C63" t="s">
         <v>336</v>
-      </c>
-      <c r="C63" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6485,9 +6483,17 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
+        <v>339</v>
+      </c>
+      <c r="C66" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
         <v>340</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>341</v>
       </c>
     </row>
@@ -6516,7 +6522,7 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>343</v>
       </c>
     </row>
@@ -6526,45 +6532,45 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="46" t="s">
         <v>345</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="46" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>348</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>349</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="48">
         <v>1796086</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="49">
         <v>0.40799999999999997</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="50">
         <f>D7*E7</f>
         <v>732803.08799999999</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="52">
         <f>SUM(F7:F7)</f>
         <v>732803.08799999999</v>
       </c>
@@ -6575,61 +6581,61 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="47" t="s">
         <v>352</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="53">
         <f>F8</f>
         <v>732803.08799999999</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="48">
         <v>44705</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="14" x14ac:dyDescent="0.3">
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="51" t="s">
         <v>354</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="52">
         <f>C11+C12</f>
         <v>777508.08799999999</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="54" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>356</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="55">
         <f>'DCF Model'!C15</f>
         <v>47833719783</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="52">
         <f>ROUND(C13/C16*1000000,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="45" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="45" t="s">
         <v>359</v>
       </c>
     </row>
